--- a/src/test/resources/companies.xlsx
+++ b/src/test/resources/companies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e130d53063b6bb12/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amank\Downloads\Student\Student\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{4CC9DF49-9B4A-41EE-81E7-C93D5A033C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4894763B-8DFB-4F73-85CB-72E5D32DAAFA}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EDF1316-4286-40E9-94A7-82CC13BD7023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0A4C0211-FE6E-408A-8FFD-81CE73164B61}"/>
   </bookViews>
@@ -57,10 +57,10 @@
     <t>accenture</t>
   </si>
   <si>
-    <t>oracle</t>
-  </si>
-  <si>
     <t>remarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tcs </t>
   </si>
 </sst>
 </file>
@@ -130,10 +130,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -453,7 +449,7 @@
         <v>2</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -505,7 +501,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3">
         <v>45340</v>
